--- a/files/STable-7.xlsx
+++ b/files/STable-7.xlsx
@@ -428,10 +428,10 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>55.30084366296536</v>
+        <v>55.30084366296528</v>
       </c>
       <c r="C2">
-        <v>63.97177985309113</v>
+        <v>63.97177985309102</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -439,10 +439,10 @@
         <v>4</v>
       </c>
       <c r="B3">
-        <v>56.18285115402914</v>
+        <v>56.18285115402919</v>
       </c>
       <c r="C3">
-        <v>64.88670222919211</v>
+        <v>64.88670222919218</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -450,10 +450,10 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>13.63388034816625</v>
+        <v>13.6338803481663</v>
       </c>
       <c r="C4">
-        <v>19.2281382143223</v>
+        <v>19.22813821432237</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -461,7 +461,7 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>19.26731994382405</v>
+        <v>19.26731994382404</v>
       </c>
       <c r="C5">
         <v>24.47890787142909</v>
@@ -513,7 +513,7 @@
         <v>2</v>
       </c>
       <c r="D2">
-        <v>0.4253682294756332</v>
+        <v>0.4253682341886602</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -527,7 +527,7 @@
         <v>3</v>
       </c>
       <c r="D3">
-        <v>0.4310925063838408</v>
+        <v>0.4310925114384904</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -541,7 +541,7 @@
         <v>4</v>
       </c>
       <c r="D4">
-        <v>0.4492185331334681</v>
+        <v>0.4492185418129813</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -555,7 +555,7 @@
         <v>5</v>
       </c>
       <c r="D5">
-        <v>0.3306514511900825</v>
+        <v>0.3306515918339185</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -569,7 +569,7 @@
         <v>6</v>
       </c>
       <c r="D6">
-        <v>0.3271135311332531</v>
+        <v>0.3271136810950708</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -583,7 +583,7 @@
         <v>7</v>
       </c>
       <c r="D7">
-        <v>0.3384955813494585</v>
+        <v>0.338495698822334</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -597,7 +597,7 @@
         <v>8</v>
       </c>
       <c r="D8">
-        <v>0.2843019530407637</v>
+        <v>0.284301909982293</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -611,7 +611,7 @@
         <v>9</v>
       </c>
       <c r="D9">
-        <v>0.2577965819736132</v>
+        <v>0.25779652104735</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -625,7 +625,7 @@
         <v>10</v>
       </c>
       <c r="D10">
-        <v>0.2416660727780103</v>
+        <v>0.241666073477913</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -639,7 +639,7 @@
         <v>2</v>
       </c>
       <c r="D11">
-        <v>0.5278998829461367</v>
+        <v>0.5278998759850988</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -653,7 +653,7 @@
         <v>3</v>
       </c>
       <c r="D12">
-        <v>0.4084372633952442</v>
+        <v>0.4084372688213639</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -667,7 +667,7 @@
         <v>4</v>
       </c>
       <c r="D13">
-        <v>0.4492185331334681</v>
+        <v>0.4492185418129813</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -681,7 +681,7 @@
         <v>5</v>
       </c>
       <c r="D14">
-        <v>0.3830271687466106</v>
+        <v>0.3830270800737191</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -695,7 +695,7 @@
         <v>6</v>
       </c>
       <c r="D15">
-        <v>0.3597026074060879</v>
+        <v>0.3597024054891498</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -709,7 +709,7 @@
         <v>7</v>
       </c>
       <c r="D16">
-        <v>0.3338741972529292</v>
+        <v>0.3338739077207593</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -723,7 +723,7 @@
         <v>8</v>
       </c>
       <c r="D17">
-        <v>0.314407691605735</v>
+        <v>0.3144073858572979</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -737,7 +737,7 @@
         <v>9</v>
       </c>
       <c r="D18">
-        <v>0.2739431876662947</v>
+        <v>0.2739427478222337</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -751,7 +751,7 @@
         <v>10</v>
       </c>
       <c r="D19">
-        <v>0.275477393426326</v>
+        <v>0.2754769686276283</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -765,7 +765,7 @@
         <v>2</v>
       </c>
       <c r="D20">
-        <v>0.4253682294756332</v>
+        <v>0.4253682341886602</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -779,7 +779,7 @@
         <v>3</v>
       </c>
       <c r="D21">
-        <v>0.4310925063838408</v>
+        <v>0.4310925114384904</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -793,7 +793,7 @@
         <v>4</v>
       </c>
       <c r="D22">
-        <v>0.2977902372053894</v>
+        <v>0.2977902239844859</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -807,7 +807,7 @@
         <v>5</v>
       </c>
       <c r="D23">
-        <v>0.3373955599598462</v>
+        <v>0.3373955474492946</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -821,7 +821,7 @@
         <v>6</v>
       </c>
       <c r="D24">
-        <v>0.3283750340581941</v>
+        <v>0.3283749211602925</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -835,7 +835,7 @@
         <v>7</v>
       </c>
       <c r="D25">
-        <v>0.3496847090962381</v>
+        <v>0.3496845121704366</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -849,7 +849,7 @@
         <v>8</v>
       </c>
       <c r="D26">
-        <v>0.3115083888514102</v>
+        <v>0.3115086203130533</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -863,7 +863,7 @@
         <v>9</v>
       </c>
       <c r="D27">
-        <v>0.2894934333804793</v>
+        <v>0.2894936381831027</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -877,7 +877,7 @@
         <v>10</v>
       </c>
       <c r="D28">
-        <v>0.2962367117528781</v>
+        <v>0.2962368825160971</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1293,7 +1293,7 @@
         <v>2</v>
       </c>
       <c r="D2">
-        <v>0.5278998829461367</v>
+        <v>0.5278998759850988</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1307,7 +1307,7 @@
         <v>4</v>
       </c>
       <c r="D3">
-        <v>0.4492185331334681</v>
+        <v>0.4492185418129813</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1321,7 +1321,7 @@
         <v>3</v>
       </c>
       <c r="D4">
-        <v>0.4310925063838408</v>
+        <v>0.4310925114384904</v>
       </c>
     </row>
     <row r="5" spans="1:4">
